--- a/backend/data/financials_by_company/1334.HK.xlsx
+++ b/backend/data/financials_by_company/1334.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,208 +682,124 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-1689150.322841</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.305287</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38317000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-5533000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-5533000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>11729000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>301214000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>32784000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>21055000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-5149000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6187000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1038000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>14172849.677159</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>406559000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>434767760</v>
-      </c>
-      <c r="T2" t="n">
-        <v>434767760</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.0238</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.0238</v>
-      </c>
-      <c r="W2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10329000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4539000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>14868000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-12150000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-5696000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>406000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>14909000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5696000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-5149000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6187000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1038000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>37629000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>105345000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-3589000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>31561000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>77758000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>27408000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>50350000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>142974000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>301214000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>444188000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>444188000</v>
-      </c>
+        <v>1976000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>3560000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3560000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>406000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1069992.071725</v>
+        <v>-2271472.698413</v>
       </c>
       <c r="C3" t="n">
-        <v>0.181817</v>
+        <v>0.171587</v>
       </c>
       <c r="D3" t="n">
-        <v>89538000</v>
+        <v>68396000</v>
       </c>
       <c r="E3" t="n">
-        <v>-5885000</v>
+        <v>-13238000</v>
       </c>
       <c r="F3" t="n">
-        <v>-5885000</v>
+        <v>-13238000</v>
       </c>
       <c r="G3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="H3" t="n">
-        <v>10252000</v>
+        <v>7312000</v>
       </c>
       <c r="I3" t="n">
-        <v>352581000</v>
+        <v>286057000</v>
       </c>
       <c r="J3" t="n">
-        <v>83653000</v>
+        <v>55158000</v>
       </c>
       <c r="K3" t="n">
-        <v>73401000</v>
+        <v>47846000</v>
       </c>
       <c r="L3" t="n">
-        <v>-5345000</v>
+        <v>-3504000</v>
       </c>
       <c r="M3" t="n">
-        <v>5921000</v>
+        <v>3746000</v>
       </c>
       <c r="N3" t="n">
-        <v>576000</v>
+        <v>242000</v>
       </c>
       <c r="O3" t="n">
-        <v>60026007.928275</v>
+        <v>47499527.301587</v>
       </c>
       <c r="P3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="Q3" t="n">
-        <v>455529000</v>
+        <v>359106000</v>
       </c>
       <c r="R3" t="n">
-        <v>15000</v>
+        <v>315000</v>
       </c>
       <c r="S3" t="n">
         <v>500000000</v>
@@ -892,156 +808,156 @@
         <v>500000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.110422</v>
+        <v>0.07306600000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.110422</v>
+        <v>0.07306600000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="X3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="AC3" t="n">
-        <v>55211000</v>
+        <v>36533000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12269000</v>
+        <v>7567000</v>
       </c>
       <c r="AE3" t="n">
-        <v>67480000</v>
+        <v>44100000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-9950000</v>
+        <v>869000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5885000</v>
+        <v>-13238000</v>
       </c>
       <c r="AH3" t="n">
-        <v>12632000</v>
+        <v>9367000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5885000</v>
+        <v>3871000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5345000</v>
+        <v>-3504000</v>
       </c>
       <c r="AK3" t="n">
-        <v>5921000</v>
+        <v>3746000</v>
       </c>
       <c r="AL3" t="n">
-        <v>576000</v>
+        <v>242000</v>
       </c>
       <c r="AM3" t="n">
-        <v>88600000</v>
+        <v>59967000</v>
       </c>
       <c r="AN3" t="n">
-        <v>102948000</v>
+        <v>73049000</v>
       </c>
       <c r="AO3" t="n">
-        <v>12632000</v>
+        <v>9367000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5621000</v>
+        <v>3519000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5621000</v>
+        <v>3519000</v>
       </c>
       <c r="AR3" t="n">
-        <v>37963000</v>
+        <v>25084000</v>
       </c>
       <c r="AS3" t="n">
-        <v>66082000</v>
+        <v>18480000</v>
       </c>
       <c r="AT3" t="n">
-        <v>24803000</v>
+        <v>10338000</v>
       </c>
       <c r="AU3" t="n">
-        <v>41279000</v>
+        <v>8142000</v>
       </c>
       <c r="AV3" t="n">
-        <v>15000</v>
+        <v>315000</v>
       </c>
       <c r="AW3" t="n">
-        <v>191548000</v>
+        <v>133016000</v>
       </c>
       <c r="AX3" t="n">
-        <v>352581000</v>
+        <v>286057000</v>
       </c>
       <c r="AY3" t="n">
-        <v>544129000</v>
+        <v>419073000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>544129000</v>
+        <v>419073000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-664214.444444</v>
+        <v>-3366702.326615</v>
       </c>
       <c r="C4" t="n">
-        <v>0.171587</v>
+        <v>0.181817</v>
       </c>
       <c r="D4" t="n">
-        <v>59029000</v>
+        <v>102170000</v>
       </c>
       <c r="E4" t="n">
-        <v>-3871000</v>
+        <v>-18517000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3871000</v>
+        <v>-18517000</v>
       </c>
       <c r="G4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="H4" t="n">
-        <v>7312000</v>
+        <v>10252000</v>
       </c>
       <c r="I4" t="n">
-        <v>286057000</v>
+        <v>352581000</v>
       </c>
       <c r="J4" t="n">
-        <v>55158000</v>
+        <v>83653000</v>
       </c>
       <c r="K4" t="n">
-        <v>47846000</v>
+        <v>73401000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3504000</v>
+        <v>-5345000</v>
       </c>
       <c r="M4" t="n">
-        <v>3746000</v>
+        <v>5921000</v>
       </c>
       <c r="N4" t="n">
-        <v>242000</v>
+        <v>576000</v>
       </c>
       <c r="O4" t="n">
-        <v>39739785.555556</v>
+        <v>70361297.67338499</v>
       </c>
       <c r="P4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="Q4" t="n">
-        <v>359106000</v>
+        <v>455529000</v>
       </c>
       <c r="R4" t="n">
-        <v>315000</v>
+        <v>15000</v>
       </c>
       <c r="S4" t="n">
         <v>500000000</v>
@@ -1050,258 +966,398 @@
         <v>500000000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07306600000000001</v>
+        <v>0.110422</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07306600000000001</v>
+        <v>0.110422</v>
       </c>
       <c r="W4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="X4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="AC4" t="n">
-        <v>36533000</v>
+        <v>55211000</v>
       </c>
       <c r="AD4" t="n">
-        <v>7567000</v>
+        <v>12269000</v>
       </c>
       <c r="AE4" t="n">
-        <v>44100000</v>
+        <v>67480000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-8498000</v>
+        <v>2682000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3871000</v>
+        <v>-18517000</v>
       </c>
       <c r="AH4" t="n">
-        <v>9367000</v>
+        <v>12632000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3871000</v>
+        <v>5885000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-3504000</v>
+        <v>-5345000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3746000</v>
+        <v>5921000</v>
       </c>
       <c r="AL4" t="n">
-        <v>242000</v>
+        <v>576000</v>
       </c>
       <c r="AM4" t="n">
-        <v>59967000</v>
+        <v>88600000</v>
       </c>
       <c r="AN4" t="n">
-        <v>73049000</v>
+        <v>102948000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9367000</v>
+        <v>12632000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3519000</v>
+        <v>5621000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3519000</v>
+        <v>5621000</v>
       </c>
       <c r="AR4" t="n">
-        <v>25084000</v>
+        <v>37963000</v>
       </c>
       <c r="AS4" t="n">
-        <v>18480000</v>
+        <v>66082000</v>
       </c>
       <c r="AT4" t="n">
-        <v>10338000</v>
+        <v>24803000</v>
       </c>
       <c r="AU4" t="n">
-        <v>8142000</v>
+        <v>41279000</v>
       </c>
       <c r="AV4" t="n">
-        <v>315000</v>
+        <v>15000</v>
       </c>
       <c r="AW4" t="n">
-        <v>133016000</v>
+        <v>191548000</v>
       </c>
       <c r="AX4" t="n">
-        <v>286057000</v>
+        <v>352581000</v>
       </c>
       <c r="AY4" t="n">
-        <v>419073000</v>
+        <v>544129000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>419073000</v>
+        <v>544129000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1613205.293884</v>
+        <v>-6240667.070218</v>
       </c>
       <c r="C5" t="n">
-        <v>0.249221</v>
+        <v>0.305287</v>
       </c>
       <c r="D5" t="n">
-        <v>21627000</v>
+        <v>53226000</v>
       </c>
       <c r="E5" t="n">
-        <v>6473000</v>
+        <v>-20442000</v>
       </c>
       <c r="F5" t="n">
-        <v>6473000</v>
+        <v>-20442000</v>
       </c>
       <c r="G5" t="n">
-        <v>13423000</v>
+        <v>10329000</v>
       </c>
       <c r="H5" t="n">
-        <v>7170000</v>
+        <v>11729000</v>
       </c>
       <c r="I5" t="n">
-        <v>177146000</v>
+        <v>301214000</v>
       </c>
       <c r="J5" t="n">
-        <v>28100000</v>
+        <v>32784000</v>
       </c>
       <c r="K5" t="n">
-        <v>20930000</v>
+        <v>21055000</v>
       </c>
       <c r="L5" t="n">
-        <v>-3001000</v>
+        <v>-5149000</v>
       </c>
       <c r="M5" t="n">
-        <v>3287000</v>
+        <v>6187000</v>
       </c>
       <c r="N5" t="n">
-        <v>286000</v>
+        <v>1038000</v>
       </c>
       <c r="O5" t="n">
-        <v>8563205.293884</v>
+        <v>24530332.929782</v>
       </c>
       <c r="P5" t="n">
-        <v>13423000</v>
+        <v>10329000</v>
       </c>
       <c r="Q5" t="n">
-        <v>229834000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>406000</v>
-      </c>
+        <v>406559000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
+        <v>434767760</v>
+      </c>
+      <c r="T5" t="n">
+        <v>434767760</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="W5" t="n">
+        <v>10329000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10329000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10329000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10329000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10329000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4539000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>14868000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2796000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-20605000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>14909000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5696000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-5149000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>6187000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1038000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>37629000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>105345000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-3589000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>31561000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>77758000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>27408000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>50350000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>142974000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>301214000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>444188000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>444188000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-2354211.801731</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.272541</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31818000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-8638000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-8638000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5016000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11246000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>353832000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23180000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11934000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-3702000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5579000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1877000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11299788.198269</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5016000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>483871000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>500000000</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>500000000</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.026846</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.026846</v>
-      </c>
-      <c r="W5" t="n">
-        <v>13423000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>13423000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13423000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>177000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>13246000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>13246000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4397000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>17643000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-4038000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>6473000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-3100000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-3373000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-3001000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3287000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>286000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>18210000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>52688000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>5076000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3560000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3560000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18658000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>16310000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8827000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7483000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>406000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>70898000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>177146000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>248044000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>248044000</v>
+      <c r="U6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5016000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5016000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5016000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>393000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4623000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4623000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1732000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6355000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>389000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-7923000</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>7923000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-3702000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5579000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1877000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>18088000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>130039000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-3935000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>32316000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>102702000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>35726000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>66976000</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>148127000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>353832000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>501959000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>501959000</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,203 +1703,83 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>114137000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>347430000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>493204000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>254470000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>347430000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8979000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>388046000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>388046000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>388346000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>388046000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>215992000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>99837000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>36000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>338604000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7404000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>7404000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7404000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>331200000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>106733000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>105158000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>177788000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>9584000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13774000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>154430000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>726950000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>141280000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3276000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18632000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>18632000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>793000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>793000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>10639000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>40616000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>40616000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>67324000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-66691000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>134015000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7327000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>41646000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>85042000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>585670000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>19629000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>39254000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>52040000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9799000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>35637000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6604000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>97148000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>236909000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-16908000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>253817000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>139260000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>52576000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>9350000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>129910000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>129910000</v>
-      </c>
+        <v>7000000</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>500000000</v>
@@ -1852,50 +1788,48 @@
         <v>500000000</v>
       </c>
       <c r="D3" t="n">
-        <v>76166000</v>
+        <v>57210000</v>
       </c>
       <c r="E3" t="n">
-        <v>126244000</v>
+        <v>78600000</v>
       </c>
       <c r="F3" t="n">
-        <v>255890000</v>
+        <v>201260000</v>
       </c>
       <c r="G3" t="n">
-        <v>416991000</v>
+        <v>319090000</v>
       </c>
       <c r="H3" t="n">
-        <v>209011000</v>
+        <v>140905000</v>
       </c>
       <c r="I3" t="n">
-        <v>255890000</v>
+        <v>201260000</v>
       </c>
       <c r="J3" t="n">
-        <v>4408000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>295155000</v>
+        <v>240490000</v>
       </c>
       <c r="L3" t="n">
-        <v>334655000</v>
+        <v>264490000</v>
       </c>
       <c r="M3" t="n">
-        <v>295155000</v>
+        <v>240490000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>295155000</v>
+        <v>240490000</v>
       </c>
       <c r="P3" t="n">
-        <v>-2645000</v>
+        <v>-2316000</v>
       </c>
       <c r="Q3" t="n">
-        <v>229582000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+        <v>174371000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -1903,145 +1837,145 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>400482000</v>
+        <v>352033000</v>
       </c>
       <c r="V3" t="n">
-        <v>41404000</v>
+        <v>24000000</v>
       </c>
       <c r="W3" t="n">
-        <v>41404000</v>
+        <v>24000000</v>
       </c>
       <c r="X3" t="n">
-        <v>1904000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>39500000</v>
+        <v>24000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>359078000</v>
+        <v>328033000</v>
       </c>
       <c r="AA3" t="n">
-        <v>84840000</v>
+        <v>54600000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2504000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>82336000</v>
+        <v>54600000</v>
       </c>
       <c r="AD3" t="n">
-        <v>175845000</v>
+        <v>166927000</v>
       </c>
       <c r="AE3" t="n">
-        <v>8107000</v>
+        <v>3611000</v>
       </c>
       <c r="AF3" t="n">
-        <v>18391000</v>
+        <v>36522000</v>
       </c>
       <c r="AG3" t="n">
-        <v>149347000</v>
+        <v>126794000</v>
       </c>
       <c r="AH3" t="n">
-        <v>695637000</v>
+        <v>592523000</v>
       </c>
       <c r="AI3" t="n">
-        <v>127548000</v>
+        <v>123585000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3028000</v>
+        <v>1965000</v>
       </c>
       <c r="AK3" t="n">
-        <v>14355000</v>
+        <v>14684000</v>
       </c>
       <c r="AL3" t="n">
-        <v>14355000</v>
+        <v>14684000</v>
       </c>
       <c r="AM3" t="n">
-        <v>722000</v>
+        <v>662000</v>
       </c>
       <c r="AN3" t="n">
-        <v>722000</v>
+        <v>662000</v>
       </c>
       <c r="AO3" t="n">
-        <v>11119000</v>
+        <v>11598000</v>
       </c>
       <c r="AP3" t="n">
-        <v>39265000</v>
+        <v>39230000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>39265000</v>
+        <v>39230000</v>
       </c>
       <c r="AR3" t="n">
-        <v>59059000</v>
+        <v>55446000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-63130000</v>
+        <v>-55197000</v>
       </c>
       <c r="AT3" t="n">
-        <v>122189000</v>
+        <v>110643000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1858000</v>
+        <v>1399000</v>
       </c>
       <c r="AV3" t="n">
-        <v>39121000</v>
+        <v>35741000</v>
       </c>
       <c r="AW3" t="n">
-        <v>81210000</v>
+        <v>73503000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>568089000</v>
+        <v>468938000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2650000</v>
+        <v>446000</v>
       </c>
       <c r="BA3" t="n">
-        <v>21457000</v>
+        <v>5810000</v>
       </c>
       <c r="BB3" t="n">
-        <v>42769000</v>
+        <v>33844000</v>
       </c>
       <c r="BC3" t="n">
-        <v>66742000</v>
+        <v>53128000</v>
       </c>
       <c r="BD3" t="n">
-        <v>3983000</v>
+        <v>26216000</v>
       </c>
       <c r="BE3" t="n">
-        <v>55629000</v>
+        <v>19340000</v>
       </c>
       <c r="BF3" t="n">
-        <v>7130000</v>
+        <v>7572000</v>
       </c>
       <c r="BG3" t="n">
-        <v>112824000</v>
+        <v>89554000</v>
       </c>
       <c r="BH3" t="n">
-        <v>275977000</v>
+        <v>264766000</v>
       </c>
       <c r="BI3" t="n">
-        <v>-9193000</v>
+        <v>-5155000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>285170000</v>
+        <v>269921000</v>
       </c>
       <c r="BK3" t="n">
-        <v>45670000</v>
+        <v>21390000</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
-        <v>45670000</v>
+        <v>21390000</v>
       </c>
       <c r="BN3" t="n">
-        <v>45670000</v>
+        <v>21390000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>500000000</v>
@@ -2050,48 +1984,50 @@
         <v>500000000</v>
       </c>
       <c r="D4" t="n">
-        <v>57210000</v>
+        <v>76166000</v>
       </c>
       <c r="E4" t="n">
-        <v>78600000</v>
+        <v>126244000</v>
       </c>
       <c r="F4" t="n">
-        <v>201260000</v>
+        <v>255890000</v>
       </c>
       <c r="G4" t="n">
-        <v>319090000</v>
+        <v>416991000</v>
       </c>
       <c r="H4" t="n">
-        <v>140905000</v>
+        <v>209011000</v>
       </c>
       <c r="I4" t="n">
-        <v>201260000</v>
+        <v>255890000</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4408000</v>
       </c>
       <c r="K4" t="n">
-        <v>240490000</v>
+        <v>295155000</v>
       </c>
       <c r="L4" t="n">
-        <v>264490000</v>
+        <v>334655000</v>
       </c>
       <c r="M4" t="n">
-        <v>240490000</v>
+        <v>295155000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>240490000</v>
+        <v>295155000</v>
       </c>
       <c r="P4" t="n">
-        <v>-2316000</v>
+        <v>-2645000</v>
       </c>
       <c r="Q4" t="n">
-        <v>174371000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>229582000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -2099,145 +2035,145 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>352033000</v>
+        <v>400482000</v>
       </c>
       <c r="V4" t="n">
-        <v>24000000</v>
+        <v>41404000</v>
       </c>
       <c r="W4" t="n">
-        <v>24000000</v>
+        <v>41404000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1904000</v>
       </c>
       <c r="Y4" t="n">
-        <v>24000000</v>
+        <v>39500000</v>
       </c>
       <c r="Z4" t="n">
-        <v>328033000</v>
+        <v>359078000</v>
       </c>
       <c r="AA4" t="n">
-        <v>54600000</v>
+        <v>84840000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2504000</v>
       </c>
       <c r="AC4" t="n">
-        <v>54600000</v>
+        <v>82336000</v>
       </c>
       <c r="AD4" t="n">
-        <v>166927000</v>
+        <v>175845000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3611000</v>
+        <v>8107000</v>
       </c>
       <c r="AF4" t="n">
-        <v>36522000</v>
+        <v>18391000</v>
       </c>
       <c r="AG4" t="n">
-        <v>126794000</v>
+        <v>149347000</v>
       </c>
       <c r="AH4" t="n">
-        <v>592523000</v>
+        <v>695637000</v>
       </c>
       <c r="AI4" t="n">
-        <v>123585000</v>
+        <v>127548000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1965000</v>
+        <v>3028000</v>
       </c>
       <c r="AK4" t="n">
-        <v>14684000</v>
+        <v>14355000</v>
       </c>
       <c r="AL4" t="n">
-        <v>14684000</v>
+        <v>14355000</v>
       </c>
       <c r="AM4" t="n">
-        <v>662000</v>
+        <v>722000</v>
       </c>
       <c r="AN4" t="n">
-        <v>662000</v>
+        <v>722000</v>
       </c>
       <c r="AO4" t="n">
-        <v>11598000</v>
+        <v>11119000</v>
       </c>
       <c r="AP4" t="n">
-        <v>39230000</v>
+        <v>39265000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>39230000</v>
+        <v>39265000</v>
       </c>
       <c r="AR4" t="n">
-        <v>55446000</v>
+        <v>59059000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-55197000</v>
+        <v>-63130000</v>
       </c>
       <c r="AT4" t="n">
-        <v>110643000</v>
+        <v>122189000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1399000</v>
+        <v>1858000</v>
       </c>
       <c r="AV4" t="n">
-        <v>35741000</v>
+        <v>39121000</v>
       </c>
       <c r="AW4" t="n">
-        <v>73503000</v>
+        <v>81210000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>468938000</v>
+        <v>568089000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>446000</v>
+        <v>2650000</v>
       </c>
       <c r="BA4" t="n">
-        <v>5810000</v>
+        <v>21457000</v>
       </c>
       <c r="BB4" t="n">
-        <v>33844000</v>
+        <v>42769000</v>
       </c>
       <c r="BC4" t="n">
-        <v>53128000</v>
+        <v>66742000</v>
       </c>
       <c r="BD4" t="n">
-        <v>26216000</v>
+        <v>3983000</v>
       </c>
       <c r="BE4" t="n">
-        <v>19340000</v>
+        <v>55629000</v>
       </c>
       <c r="BF4" t="n">
-        <v>7572000</v>
+        <v>7130000</v>
       </c>
       <c r="BG4" t="n">
-        <v>89554000</v>
+        <v>112824000</v>
       </c>
       <c r="BH4" t="n">
-        <v>264766000</v>
+        <v>275977000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-5155000</v>
+        <v>-9193000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>269921000</v>
+        <v>285170000</v>
       </c>
       <c r="BK4" t="n">
-        <v>21390000</v>
+        <v>45670000</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>21390000</v>
+        <v>45670000</v>
       </c>
       <c r="BN4" t="n">
-        <v>21390000</v>
+        <v>45670000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>500000000</v>
@@ -2245,192 +2181,388 @@
       <c r="C5" t="n">
         <v>500000000</v>
       </c>
-      <c r="D5" t="n">
-        <v>52576000</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>65748000</v>
+        <v>114137000</v>
       </c>
       <c r="F5" t="n">
-        <v>165644000</v>
+        <v>347430000</v>
       </c>
       <c r="G5" t="n">
-        <v>271634000</v>
+        <v>493204000</v>
       </c>
       <c r="H5" t="n">
-        <v>108017000</v>
+        <v>254470000</v>
       </c>
       <c r="I5" t="n">
-        <v>165644000</v>
+        <v>347430000</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>8979000</v>
       </c>
       <c r="K5" t="n">
-        <v>205886000</v>
+        <v>388046000</v>
       </c>
       <c r="L5" t="n">
-        <v>238886000</v>
+        <v>388046000</v>
       </c>
       <c r="M5" t="n">
-        <v>205886000</v>
+        <v>388346000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="O5" t="n">
-        <v>205886000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+        <v>388046000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>137838000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>215992000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>99837000</v>
+      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="U5" t="n">
-        <v>215945000</v>
+        <v>338604000</v>
       </c>
       <c r="V5" t="n">
-        <v>33000000</v>
+        <v>7404000</v>
       </c>
       <c r="W5" t="n">
-        <v>33000000</v>
+        <v>7404000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>7404000</v>
       </c>
       <c r="Y5" t="n">
-        <v>33000000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>182945000</v>
+        <v>331200000</v>
       </c>
       <c r="AA5" t="n">
-        <v>32748000</v>
+        <v>106733000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1575000</v>
       </c>
       <c r="AC5" t="n">
-        <v>32748000</v>
+        <v>105158000</v>
       </c>
       <c r="AD5" t="n">
-        <v>119348000</v>
+        <v>177788000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1539000</v>
+        <v>9584000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11211000</v>
+        <v>13774000</v>
       </c>
       <c r="AG5" t="n">
-        <v>106598000</v>
+        <v>154430000</v>
       </c>
       <c r="AH5" t="n">
-        <v>421831000</v>
+        <v>726950000</v>
       </c>
       <c r="AI5" t="n">
-        <v>130869000</v>
+        <v>141280000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1231000</v>
+        <v>3276000</v>
       </c>
       <c r="AK5" t="n">
-        <v>17000000</v>
+        <v>18632000</v>
       </c>
       <c r="AL5" t="n">
-        <v>17000000</v>
+        <v>18632000</v>
       </c>
       <c r="AM5" t="n">
-        <v>656000</v>
+        <v>793000</v>
       </c>
       <c r="AN5" t="n">
-        <v>656000</v>
+        <v>793000</v>
       </c>
       <c r="AO5" t="n">
-        <v>12077000</v>
+        <v>10639000</v>
       </c>
       <c r="AP5" t="n">
-        <v>40242000</v>
+        <v>40616000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>40242000</v>
+        <v>40616000</v>
       </c>
       <c r="AR5" t="n">
-        <v>59663000</v>
+        <v>67324000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-50336000</v>
+        <v>-66691000</v>
       </c>
       <c r="AT5" t="n">
-        <v>109999000</v>
+        <v>134015000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3498000</v>
+        <v>7327000</v>
       </c>
       <c r="AV5" t="n">
-        <v>33136000</v>
+        <v>41646000</v>
       </c>
       <c r="AW5" t="n">
-        <v>73365000</v>
+        <v>85042000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>290962000</v>
+        <v>585670000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>413000</v>
+        <v>1430000</v>
       </c>
       <c r="BA5" t="n">
-        <v>16230000</v>
+        <v>19629000</v>
       </c>
       <c r="BB5" t="n">
-        <v>22063000</v>
+        <v>39254000</v>
       </c>
       <c r="BC5" t="n">
-        <v>45332000</v>
+        <v>52040000</v>
       </c>
       <c r="BD5" t="n">
-        <v>31686000</v>
+        <v>9799000</v>
       </c>
       <c r="BE5" t="n">
-        <v>9086000</v>
+        <v>35637000</v>
       </c>
       <c r="BF5" t="n">
-        <v>4560000</v>
+        <v>6604000</v>
       </c>
       <c r="BG5" t="n">
-        <v>63212000</v>
+        <v>97148000</v>
       </c>
       <c r="BH5" t="n">
-        <v>123540000</v>
+        <v>236909000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-2338000</v>
+        <v>-16908000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>125878000</v>
+        <v>253817000</v>
       </c>
       <c r="BK5" t="n">
-        <v>20172000</v>
+        <v>139260000</v>
       </c>
       <c r="BL5" t="n">
-        <v>7000000</v>
+        <v>9350000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13172000</v>
+        <v>129910000</v>
       </c>
       <c r="BN5" t="n">
-        <v>13172000</v>
+        <v>129910000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>77369000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>201816000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>312690000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>567400000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>325454000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>312690000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7616000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>373200000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>477400000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>390737000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17537000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>373200000</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>201008000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>99837000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>493729000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>109959000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>109959000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5759000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>104200000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>383770000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>91857000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1857000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>260224000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>8392000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11554000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>240278000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>884466000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>175242000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3771000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>23304000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>23304000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>904000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>904000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>60510000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>60510000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>86753000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-77960000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>164713000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>19533000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>53387000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>91793000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>709224000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2047000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14793000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>54765000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>64712000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6780000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>35193000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>22739000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>108187000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>328675000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-21247000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>349922000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>136045000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>19214000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>116831000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>116831000</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2688,187 +2820,113 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Net Foreign Currency Exchange Gain Loss</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>40985000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-152036000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>135358000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>99873000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-13777000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>129910000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45670000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>122000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>84118000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>64483000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-6187000</v>
-      </c>
+        <v>-150000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-10102000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-10102000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>99873000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>99873000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-16678000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-16678000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-152036000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>135358000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-35127000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1038000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-10897000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>-10897000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>-2869000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2869000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-10749000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>159000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-10908000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>54762000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-8811000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26318000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-42645000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-6357000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>5083000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-20579000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>14702000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>76114000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5178000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11729000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>565000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11164000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-163000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>18000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>14868000</v>
-      </c>
+        <v>-19331000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>-656000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-656000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>278000</v>
+        <v>-942000</v>
       </c>
       <c r="C3" t="n">
-        <v>-79618000</v>
+        <v>-53857000</v>
       </c>
       <c r="D3" t="n">
-        <v>122854000</v>
+        <v>66709000</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-6127000</v>
+        <v>-1974000</v>
       </c>
       <c r="G3" t="n">
-        <v>45670000</v>
+        <v>21390000</v>
       </c>
       <c r="H3" t="n">
-        <v>21390000</v>
+        <v>13172000</v>
       </c>
       <c r="I3" t="n">
-        <v>3000</v>
+        <v>384000</v>
       </c>
       <c r="J3" t="n">
-        <v>24277000</v>
+        <v>7834000</v>
       </c>
       <c r="K3" t="n">
-        <v>31948000</v>
+        <v>1529000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-5921000</v>
+        <v>-3746000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -2881,28 +2939,28 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>43236000</v>
+        <v>12852000</v>
       </c>
       <c r="S3" t="n">
-        <v>43236000</v>
+        <v>12852000</v>
       </c>
       <c r="T3" t="n">
-        <v>-79618000</v>
+        <v>-53857000</v>
       </c>
       <c r="U3" t="n">
-        <v>122854000</v>
+        <v>66709000</v>
       </c>
       <c r="V3" t="n">
-        <v>-14076000</v>
+        <v>5273000</v>
       </c>
       <c r="W3" t="n">
-        <v>576000</v>
+        <v>242000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -2914,104 +2972,105 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1361000</v>
+        <v>-215000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1361000</v>
+        <v>-215000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4738000</v>
+        <v>-1754000</v>
       </c>
       <c r="AF3" t="n">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4766000</v>
+        <v>-1759000</v>
       </c>
       <c r="AH3" t="n">
-        <v>6405000</v>
+        <v>1032000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-14569000</v>
+        <v>-3355000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-67948000</v>
+        <v>-54758000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-28870000</v>
+        <v>82024000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-7288000</v>
+        <v>26490000</v>
       </c>
       <c r="AM3" t="n">
-        <v>22553000</v>
+        <v>20196000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-4932000</v>
+        <v>-8290000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-13614000</v>
+        <v>-7796000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-35797000</v>
+        <v>-167382000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5345000</v>
+        <v>3504000</v>
       </c>
       <c r="AR3" t="n">
-        <v>10252000</v>
+        <v>7312000</v>
       </c>
       <c r="AS3" t="n">
-        <v>373000</v>
+        <v>274000</v>
       </c>
       <c r="AT3" t="n">
-        <v>9879000</v>
+        <v>7038000</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>20000</v>
+        <v>364000</v>
       </c>
       <c r="AW3" t="n">
-        <v>67480000</v>
-      </c>
+        <v>44100000</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-942000</v>
+        <v>278000</v>
       </c>
       <c r="C4" t="n">
-        <v>-53857000</v>
+        <v>-79618000</v>
       </c>
       <c r="D4" t="n">
-        <v>66709000</v>
+        <v>122854000</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-1974000</v>
+        <v>-6127000</v>
       </c>
       <c r="G4" t="n">
+        <v>45670000</v>
+      </c>
+      <c r="H4" t="n">
         <v>21390000</v>
       </c>
-      <c r="H4" t="n">
-        <v>13172000</v>
-      </c>
       <c r="I4" t="n">
-        <v>384000</v>
+        <v>3000</v>
       </c>
       <c r="J4" t="n">
-        <v>7834000</v>
+        <v>24277000</v>
       </c>
       <c r="K4" t="n">
-        <v>1529000</v>
+        <v>31948000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-3746000</v>
+        <v>-5921000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -3024,28 +3083,28 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>12852000</v>
+        <v>43236000</v>
       </c>
       <c r="S4" t="n">
-        <v>12852000</v>
+        <v>43236000</v>
       </c>
       <c r="T4" t="n">
-        <v>-53857000</v>
+        <v>-79618000</v>
       </c>
       <c r="U4" t="n">
-        <v>66709000</v>
+        <v>122854000</v>
       </c>
       <c r="V4" t="n">
-        <v>5273000</v>
+        <v>-14076000</v>
       </c>
       <c r="W4" t="n">
-        <v>242000</v>
+        <v>576000</v>
       </c>
       <c r="X4" t="n">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -3057,212 +3116,358 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-215000</v>
+        <v>-1361000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-215000</v>
+        <v>-1361000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1754000</v>
+        <v>-4738000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5000</v>
+        <v>28000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1759000</v>
+        <v>-4766000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1032000</v>
+        <v>6405000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3355000</v>
+        <v>-14569000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-54758000</v>
+        <v>-67948000</v>
       </c>
       <c r="AK4" t="n">
-        <v>82024000</v>
+        <v>-28870000</v>
       </c>
       <c r="AL4" t="n">
-        <v>26490000</v>
+        <v>-7288000</v>
       </c>
       <c r="AM4" t="n">
-        <v>20196000</v>
+        <v>22553000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-8290000</v>
+        <v>-4932000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-7796000</v>
+        <v>-13614000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-167382000</v>
+        <v>-35797000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3504000</v>
+        <v>5345000</v>
       </c>
       <c r="AR4" t="n">
-        <v>7312000</v>
+        <v>10252000</v>
       </c>
       <c r="AS4" t="n">
-        <v>274000</v>
+        <v>373000</v>
       </c>
       <c r="AT4" t="n">
-        <v>7038000</v>
+        <v>9879000</v>
       </c>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>364000</v>
+        <v>20000</v>
       </c>
       <c r="AW4" t="n">
-        <v>44100000</v>
-      </c>
+        <v>67480000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-9864000</v>
+        <v>41022000</v>
       </c>
       <c r="C5" t="n">
-        <v>-37000000</v>
+        <v>-152036000</v>
       </c>
       <c r="D5" t="n">
-        <v>59748000</v>
+        <v>135358000</v>
       </c>
       <c r="E5" t="n">
-        <v>24405000</v>
+        <v>99873000</v>
       </c>
       <c r="F5" t="n">
-        <v>-4912000</v>
+        <v>-13777000</v>
       </c>
       <c r="G5" t="n">
-        <v>13172000</v>
+        <v>129910000</v>
       </c>
       <c r="H5" t="n">
-        <v>28158000</v>
+        <v>45670000</v>
       </c>
       <c r="I5" t="n">
-        <v>-40000</v>
+        <v>85000</v>
       </c>
       <c r="J5" t="n">
-        <v>-14946000</v>
+        <v>84155000</v>
       </c>
       <c r="K5" t="n">
-        <v>19280000</v>
+        <v>64483000</v>
       </c>
       <c r="L5" t="n">
-        <v>-150000</v>
+        <v>300000</v>
       </c>
       <c r="M5" t="n">
-        <v>-3287000</v>
+        <v>-6187000</v>
       </c>
       <c r="N5" t="n">
-        <v>-19331000</v>
+        <v>-10102000</v>
       </c>
       <c r="O5" t="n">
-        <v>-19331000</v>
+        <v>-10102000</v>
       </c>
       <c r="P5" t="n">
-        <v>24405000</v>
+        <v>99873000</v>
       </c>
       <c r="Q5" t="n">
-        <v>24405000</v>
+        <v>99873000</v>
       </c>
       <c r="R5" t="n">
-        <v>22748000</v>
+        <v>-16678000</v>
       </c>
       <c r="S5" t="n">
-        <v>22748000</v>
+        <v>-16678000</v>
       </c>
       <c r="T5" t="n">
-        <v>-37000000</v>
+        <v>-152036000</v>
       </c>
       <c r="U5" t="n">
-        <v>59748000</v>
+        <v>135358000</v>
       </c>
       <c r="V5" t="n">
-        <v>-29274000</v>
+        <v>-35127000</v>
       </c>
       <c r="W5" t="n">
-        <v>286000</v>
+        <v>1038000</v>
       </c>
       <c r="X5" t="n">
-        <v>-24000000</v>
-      </c>
-      <c r="Y5" t="n">
+        <v>-10897000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-10897000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>-2869000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2869000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-10749000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>159000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-10908000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>54799000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-8811000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>26318000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-42645000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-6357000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5083000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-20579000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14702000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>76114000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5178000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11729000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>565000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11164000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-163000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>14868000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-43920000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-118358000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>207400000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-27089000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>116831000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>129910000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-721000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-12358000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>65850000</v>
+      </c>
+      <c r="L6" t="n">
         <v>3000000</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-27000000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-656000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-656000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-369000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-369000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-4535000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-4543000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-4952000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-3760000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-25759000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-5455000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>4338000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>46119000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-6424000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-13392000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-50945000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-99000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7170000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>249000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6921000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>125000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17643000</v>
+      <c r="M6" t="n">
+        <v>-5579000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-19250000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-19250000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>89042000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>89042000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-118358000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>207400000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-61377000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1877000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-15579000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>-15579000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-2384000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2384000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-24470000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>235000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-24705000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-16831000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-3912000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-42697000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-9610000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-2271000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85848000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-3277000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-12672000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-100715000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3702000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11246000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>761000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10485000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>715000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>55000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6355000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-107000</v>
       </c>
     </row>
   </sheetData>
@@ -3792,177 +3997,177 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>ipoExpectedDate</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>ipoExpectedDate</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EH1" t="inlineStr">
@@ -4039,7 +4244,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Ruichang International Holdings Limited manufactures and sells petroleum refinery and petrochemical equipment in Mainland China. The company offers sulphur recovery unit and volatile organic compounds (VOCs) incineration equipment; catalytic cracking equipment; process burners; and heat exchangers. It also provides installation and technology consulting services. The company was founded in 1994 and is headquartered in Shanghai, the People's Republic of China.</t>
+          <t>Ruichang International Holdings Limited manufactures and sells petroleum refinery and petrochemical equipment in Mainland China. The company offers sulphur recovery units and volatile organic compounds (VOCs) incineration equipment; catalytic cracking equipment; process burners; and heat exchangers. It also manufactures and sells industrial products. The company was founded in 1994 and is headquartered in Shanghai, the People's Republic of China.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4047,7 +4252,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Bo  Lu', 'age': 51, 'title': 'CEO, Interim Financial Director &amp; Chairman', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 1253433, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Rui  Wu', 'age': 57, 'title': 'VP of Administration &amp; Executive Director', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 474961, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wei  Bai', 'age': 51, 'title': 'SVP of Human Resources &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 535200, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaojing  Lu', 'age': 54, 'title': 'Deputy CEO &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 960348, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Song  Shao', 'age': 55, 'title': 'Senior VP &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 834078, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xian  Zhang', 'age': 48, 'title': 'Senior Vice President of Sales/business', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xuli  Jin', 'age': 46, 'title': 'Senior Vice President of Operation Management', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Haiyang  Guo', 'title': 'Joint Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yan Ting  Kwok', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Bo  Lu', 'age': 51, 'title': 'CEO, Interim Financial Director &amp; Chairman', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 1253236, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Rui  Wu', 'age': 57, 'title': 'VP of Administration &amp; Executive Director', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 474886, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wei  Bai', 'age': 51, 'title': 'SVP of Human Resources &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 535116, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaojing  Lu', 'age': 54, 'title': 'Deputy CEO &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 960197, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Song  Shao', 'age': 55, 'title': 'Senior VP &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 833946, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xian  Zhang', 'age': 48, 'title': 'Senior Vice President of Sales/business', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xuli  Jin', 'age': 46, 'title': 'Senior Vice President of Operation Management', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Haiyang  Guo', 'title': 'Joint Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yan Ting  Kwok', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4065,28 +4270,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AC2" t="n">
         <v>0.05</v>
@@ -4101,37 +4306,37 @@
         <v>4.006</v>
       </c>
       <c r="AG2" t="n">
-        <v>119.00001</v>
+        <v>114</v>
       </c>
       <c r="AH2" t="n">
-        <v>5925000</v>
+        <v>1237500</v>
       </c>
       <c r="AI2" t="n">
-        <v>5925000</v>
+        <v>1237500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1735500</v>
+        <v>1773250</v>
       </c>
       <c r="AK2" t="n">
-        <v>4002000</v>
+        <v>1106250</v>
       </c>
       <c r="AL2" t="n">
-        <v>4002000</v>
+        <v>1106250</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AO2" t="n">
-        <v>595000000</v>
+        <v>570000000</v>
       </c>
       <c r="AP2" t="n">
-        <v>655000000</v>
+        <v>570000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR2" t="n">
         <v>2.65</v>
@@ -4143,19 +4348,19 @@
         <v>0.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.1853558</v>
+        <v>1.1355509</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.8414</v>
+        <v>1.7366</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.2756</v>
+        <v>1.28065</v>
       </c>
       <c r="AX2" t="n">
         <v>0.04</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.030534351</v>
+        <v>0.034188036</v>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
@@ -4172,13 +4377,13 @@
         <v>0.009990000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>131890000</v>
+        <v>130520000</v>
       </c>
       <c r="BE2" t="n">
         <v>500000000</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.73622</v>
+        <v>0.73896</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -4187,10 +4392,10 @@
         <v>500000000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.8641972</v>
+        <v>0.86247957</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.3770006</v>
+        <v>1.3217704</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4214,10 +4419,10 @@
         <v>50.832</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.4395604</v>
+        <v>0.12871289</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BT2" t="n">
         <v>0.05</v>
@@ -4231,7 +4436,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4332,134 +4537,134 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1720575000000</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.029999971</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>1.09 - 1.24</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1773250</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.24000001</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.26666668</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.9 - 2.65</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-1.5100001</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.56981134</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>12.871289</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>RUICHANG INTL</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
           <t>Ruichang International Holdings Limited</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>RUICHANG INTL</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>-9.160297</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DO2" t="n">
+        <v>-0.59660006</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.34354487</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.14065003</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.109827064</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>[{'header': 'Dividend', 'message': '1334.HK announced a cash dividend of HKD 0.05 with an ex-date of Jul. 6, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1783267200000, 'amount': '0.05'}}]</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1781769383</v>
+      </c>
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>finmb_1881953447</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="EC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1720575000000</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.119999886</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>1.1 - 1.32</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1735500</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.30000007</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.33707875</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>0.89 - 2.65</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.5509434</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>43.95604</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.6513999700000001</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.35375255</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.08559990000000001</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.0671056</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-2.5641003</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1.14</v>
       </c>
       <c r="EH2" t="inlineStr"/>
     </row>
